--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="410">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MedicationAdministration profile for paracetamol given because of fever.</t>
+    <t>MedicationAdministration profile for paracetamol administered because of fever.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -644,7 +644,7 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
+    <t>Procedure this administration supports</t>
   </si>
   <si>
     <t>A larger event of which this particular event is a component or step.</t>
@@ -662,7 +662,7 @@
     <t>MedicationAdministration.status</t>
   </si>
   <si>
-    <t>in-progress | not-done | on-hold | completed | entered-in-error | stopped | unknown</t>
+    <t>Medication administration status</t>
   </si>
   <si>
     <t>Will generally be set to show that the administration has been completed.  For some long running administrations such as infusions, it is possible for an administration to be started but not completed or it may be paused while some other process is under way.</t>
@@ -692,7 +692,7 @@
     <t>MedicationAdministration.statusReason</t>
   </si>
   <si>
-    <t>Reason administration not performed</t>
+    <t>Reason medication was not given or status rationale</t>
   </si>
   <si>
     <t>A code indicating why the administration was not performed.</t>
@@ -741,7 +741,7 @@
 </t>
   </si>
   <si>
-    <t>What was administered</t>
+    <t>Administered medication</t>
   </si>
   <si>
     <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -821,10 +821,10 @@
 </t>
   </si>
   <si>
-    <t>Who received medication</t>
-  </si>
-  <si>
-    <t>The person or animal or group receiving the medication.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -846,10 +846,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter administered as part of</t>
-  </si>
-  <si>
-    <t>The visit, admission, or other contact between patient and health care provider during which the medication administration was performed.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>Event.encounter</t>
@@ -887,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Specific date/time or interval of time during which the administration took place (or did not take place)</t>
+    <t>Administration date/time</t>
   </si>
   <si>
     <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
@@ -1044,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Concept, condition or observation that supports why the medication was administered</t>
+    <t>Reason or clinical trigger for administration</t>
   </si>
   <si>
     <t>A code, Condition or observation that supports why the medication was administered.</t>
@@ -1131,7 +1131,7 @@
     <t>MedicationAdministration.dosage</t>
   </si>
   <si>
-    <t>Details of how medication was taken</t>
+    <t>Dose details</t>
   </si>
   <si>
     <t>Describes the medication dosage information details e.g. dose, rate, site, route, etc.</t>
@@ -1508,98 +1508,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1785,10 +1787,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1868,7 +1870,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -883,29 +883,33 @@
     <t>MedicationAdministration.occurence[x]</t>
   </si>
   <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Administration date/time</t>
+  </si>
+  <si>
+    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.recorded</t>
+  </si>
+  <si>
     <t xml:space="preserve">dateTime
 </t>
-  </si>
-  <si>
-    <t>Administration date/time</t>
-  </si>
-  <si>
-    <t>A specific date/time or interval of time during which the administration took place (or did not take place). For many administrations, such as swallowing a tablet the use of dateTime is more appropriate.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>RXA-3 Date/Time Start of Administration / RXA-4 Date/Time End of Administration</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.recorded</t>
   </si>
   <si>
     <t>When the MedicationAdministration was first captured in the subject's record</t>
@@ -5195,13 +5199,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5270,10 +5274,10 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5281,10 +5285,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5307,13 +5311,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5364,7 +5368,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5393,10 +5397,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5422,10 +5426,10 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5456,7 +5460,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5474,7 +5478,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5503,10 +5507,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5529,13 +5533,13 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5586,7 +5590,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5601,24 +5605,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5641,7 +5645,7 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>154</v>
@@ -5727,10 +5731,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5841,14 +5845,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5870,10 +5874,10 @@
         <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>182</v>
@@ -5928,7 +5932,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5957,10 +5961,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5986,10 +5990,10 @@
         <v>172</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6019,10 +6023,10 @@
         <v>226</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6040,7 +6044,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6055,13 +6059,13 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6069,10 +6073,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6095,13 +6099,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6152,7 +6156,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>88</v>
@@ -6167,13 +6171,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6181,10 +6185,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6207,13 +6211,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6243,10 +6247,10 @@
         <v>226</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6264,7 +6268,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6279,24 +6283,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6319,16 +6323,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6378,7 +6382,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6393,24 +6397,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6433,13 +6437,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6490,7 +6494,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6511,18 +6515,18 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6545,13 +6549,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6602,7 +6606,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6617,13 +6621,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6631,10 +6635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6657,13 +6661,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6714,7 +6718,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6726,7 +6730,7 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6735,7 +6739,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6743,10 +6747,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6769,7 +6773,7 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>154</v>
@@ -6855,10 +6859,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6969,14 +6973,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6998,10 +7002,10 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>182</v>
@@ -7056,7 +7060,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7085,10 +7089,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7111,13 +7115,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7168,7 +7172,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7177,7 +7181,7 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>100</v>
@@ -7189,7 +7193,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7197,10 +7201,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7226,13 +7230,13 @@
         <v>172</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7261,10 +7265,10 @@
         <v>226</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7282,7 +7286,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7303,18 +7307,18 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7340,10 +7344,10 @@
         <v>172</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7373,10 +7377,10 @@
         <v>226</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7394,7 +7398,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7415,18 +7419,18 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7452,13 +7456,13 @@
         <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7487,10 +7491,10 @@
         <v>226</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7508,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7529,18 +7533,18 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7563,16 +7567,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7622,7 +7626,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7631,7 +7635,7 @@
         <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>100</v>
@@ -7643,18 +7647,18 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7677,16 +7681,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7736,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7745,7 +7749,7 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
@@ -7757,18 +7761,18 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7791,16 +7795,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7850,7 +7854,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7871,7 +7875,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
+++ b/StructureDefinition-paracetamol-on-fever-medicationAdministration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
